--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.55848187991</v>
+        <v>2.040753305485375</v>
       </c>
       <c r="D2" t="n">
-        <v>8.40155746278351</v>
+        <v>1.36525308770232</v>
       </c>
       <c r="E2" t="n">
-        <v>9.171335996511564</v>
+        <v>1.490342099433129</v>
       </c>
       <c r="F2" t="n">
-        <v>11.01165942908875</v>
+        <v>1.789394657226922</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.19852001051961</v>
+        <v>3.607259501709437</v>
       </c>
       <c r="D3" t="n">
-        <v>11.68951237419615</v>
+        <v>1.899545760806875</v>
       </c>
       <c r="E3" t="n">
-        <v>9.171335996511564</v>
+        <v>1.490342099433129</v>
       </c>
       <c r="F3" t="n">
-        <v>11.01165942908875</v>
+        <v>1.789394657226922</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.31824016572275</v>
+        <v>2.651714026929947</v>
       </c>
       <c r="D4" t="n">
-        <v>16.45226670869202</v>
+        <v>2.673493340162454</v>
       </c>
       <c r="E4" t="n">
-        <v>9.171335996511564</v>
+        <v>1.490342099433129</v>
       </c>
       <c r="F4" t="n">
-        <v>11.01165942908875</v>
+        <v>1.789394657226922</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.59930430673971</v>
+        <v>5.134886949845203</v>
       </c>
       <c r="D5" t="n">
-        <v>32.32221904293249</v>
+        <v>5.25236059447653</v>
       </c>
       <c r="E5" t="n">
-        <v>9.171335996511564</v>
+        <v>1.490342099433129</v>
       </c>
       <c r="F5" t="n">
-        <v>11.01165942908875</v>
+        <v>1.789394657226922</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.16196395802455</v>
+        <v>7.17631914317899</v>
       </c>
       <c r="D6" t="n">
-        <v>44.08140643924158</v>
+        <v>7.163228546376757</v>
       </c>
       <c r="E6" t="n">
-        <v>9.171335996511564</v>
+        <v>1.490342099433129</v>
       </c>
       <c r="F6" t="n">
-        <v>11.01165942908875</v>
+        <v>1.789394657226922</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.87323997400657</v>
+        <v>3.879401495776068</v>
       </c>
       <c r="D7" t="n">
-        <v>24.14023046713698</v>
+        <v>3.92278745090976</v>
       </c>
       <c r="E7" t="n">
-        <v>9.171335996511564</v>
+        <v>1.490342099433129</v>
       </c>
       <c r="F7" t="n">
-        <v>11.01165942908875</v>
+        <v>1.789394657226922</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.94279329051601</v>
+        <v>4.378203909708852</v>
       </c>
       <c r="D8" t="n">
-        <v>26.70222440830202</v>
+        <v>4.339111466349078</v>
       </c>
       <c r="E8" t="n">
-        <v>9.171335996511564</v>
+        <v>1.490342099433129</v>
       </c>
       <c r="F8" t="n">
-        <v>11.01165942908875</v>
+        <v>1.789394657226922</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.17465213539026</v>
+        <v>4.903380972000917</v>
       </c>
       <c r="D9" t="n">
-        <v>30.23654750724083</v>
+        <v>4.913438969926635</v>
       </c>
       <c r="E9" t="n">
-        <v>9.171335996511564</v>
+        <v>1.490342099433129</v>
       </c>
       <c r="F9" t="n">
-        <v>11.01165942908875</v>
+        <v>1.789394657226922</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
